--- a/reports/livrables/L4_analyse/q1_tableaux.xlsx
+++ b/reports/livrables/L4_analyse/q1_tableaux.xlsx
@@ -1,49 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_chiffres_cles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_canaux" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_canaux_evolution" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_mois" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_categories" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_categories_par_exercice" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_gammes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_marques" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_top_produits" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_types" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_magasins" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_pays" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_poids_facteurs_ligne" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_poids_facteurs_mois" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_correlations_pearson" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_correlations_spearman" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_correlations_cibles" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_situation" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_ratios" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_magasins_beneficiaires" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_pont_resultat_magasins" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_publicite_budget" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_publicite_tests" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_magasins_par_mois" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_categories_resultat" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_magasins_exercice" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_seuils" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_repartition_publicite" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_charges_par_compte" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_publicite_par_campagne" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_calendrier_publicite" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_regroupement_par_pays" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_baisse_publicite" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_stock_dormant" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_leviers" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_leviers_par_famille" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_grille_publicite" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="2_chiffres_cles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_canaux" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2_canaux_evolution" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3_mois" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4_categories" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4_categories_par_exercice" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="4_gammes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="4_marques" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="4_top_produits" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="5_types" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="5_magasins" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="5_pays" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="6_poids_facteurs_ligne" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="6_poids_facteurs_mois" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="6_correlations_pearson" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="6_correlations_spearman" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="6_correlations_cibles" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="7_situation" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="7_ratios" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="7_magasins_beneficiaires" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="7_pont_resultat_magasins" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="7_publicite_budget" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="7_publicite_tests" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="7_magasins_par_mois" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="7_categories_resultat" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="7_magasins_exercice" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="8_seuils" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="8_repartition_publicite" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="8_charges_par_compte" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="8_publicite_par_campagne" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="8_calendrier_publicite" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="8_regroupement_par_pays" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="8_baisse_publicite" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="8_stock_dormant" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="8_leviers" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="8_leviers_par_famille" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="8_grille_publicite" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
